--- a/quizzes/peinture-17e-niveau1.xlsx
+++ b/quizzes/peinture-17e-niveau1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86577D3-6A23-4270-B85C-3C6A3A0414BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF4616F-4A4F-4361-92B9-D04BD2125D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quiz d'art" sheetId="1" r:id="rId1"/>
@@ -64,9 +64,6 @@
     <t>Paysage avec la fuite en Égypte</t>
   </si>
   <si>
-    <t>Anthony van Dyck</t>
-  </si>
-  <si>
     <t>1635</t>
   </si>
   <si>
@@ -106,9 +103,6 @@
     <t>Mauritshuis, La Haye</t>
   </si>
   <si>
-    <t>Charles Le Brun</t>
-  </si>
-  <si>
     <t>1655-1661</t>
   </si>
   <si>
@@ -124,9 +118,6 @@
     <t>Le Débarquement de Cléopâtre à Tarse</t>
   </si>
   <si>
-    <t>David Teniers le Jeune</t>
-  </si>
-  <si>
     <t>1642</t>
   </si>
   <si>
@@ -142,9 +133,6 @@
     <t>Les Ménines</t>
   </si>
   <si>
-    <t>Eustache Le Sueur</t>
-  </si>
-  <si>
     <t>1652-1655</t>
   </si>
   <si>
@@ -316,18 +304,12 @@
     <t>La Présentation au Temple</t>
   </si>
   <si>
-    <t>Willem van de Velde le Jeune</t>
-  </si>
-  <si>
     <t>Le Canon de salut</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/9/92/Annibale_Carracci_003.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/ae/Portrait_de_Charles_1er%2C_roi_d%27Angleterre%2C_%C3%A0_la_chasse_-_Antoon_van_Dyck_-_Mus%C3%A9e_du_Louvre_Peintures_INV_1236_%3B_MR_666.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/b/b0/GENTILESCHI_Judith.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
@@ -340,30 +322,18 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/6/60/Charles_Le_Brun_-_Pierre_S%C3%A9guier%2C_chancelier_de_France_%281655-1661%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/0/0a/David_Teniers_%28II%29_-_Smoker_Leaning_his_Elbow_on_a_Table_-_WGA22080.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/b/b1/Las_Meninas%2C_by_Diego_Vel%C3%A1zquez%2C_from_Prado_in_Google_EarthFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/a/ad/Le_Sueur%2C_Eustache_-_Melpom%C3%A8ne%2C_%C3%89rato_et_Polymnie_-_1652_-_1655.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/e/ef/Francisco_de_Zurbar%C3%A1n_006.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/97/Cavalier_soldier_Hals-1624x.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/f/fe/Woman_Reading_a_Letter_by_Gabri%C3%ABl_Metsu.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/91/La_Tour_Le_Tricheur_Louvre_RF1972-8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/9/9f/Gerard_Dou_-_The_Dropsical_Woman_-_WGA06647.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -373,30 +343,15 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/8/8d/Autoportrait_au_turban_%28Perpignan%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/8f/Jordaens_King_Drinks_1638-40.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/7/74/Jacob_Isaacksz._van_Ruisdael_-_Le_Moulin_de_Wijk-bij-Duurstede.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/0/01/Goyen_1651_View_of_Dordrecht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Musée de Dordrecht</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0f/1665_Girl_with_a_Pearl_Earring.jpg/1920px-1665_Girl_with_a_Pearl_Earring.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/6/62/Meindert_Hobbema_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/8/82/Le_v%C5%93u_de_Louis_XIII.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -418,13 +373,58 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/e/ed/Het_Kanonschot_-_Canon_fired_%28Willem_van_de_Velde_II%2C_1707%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Caravaggio ou Caravage</t>
-  </si>
-  <si>
-    <t>Annibale Carracci ou Carrache</t>
-  </si>
-  <si>
-    <t>Guercino ou Guerchin</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/6e/Van_Dyck_Charles_I_1635.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/69/Analyasis_of_Las_Meninas.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Frans_Hals_%E2%80%93_The_Laughing_Cavalier.jpg/960px-Frans_Hals_%E2%80%93_The_Laughing_Cavalier.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/b/bc/Jacob_Jordaens_-_The_Bean_King_%28Louvre%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/01/Goyen_1651_View_of_Dordrecht.jpg/1280px-Goyen_1651_View_of_Dordrecht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/Meindert_Hobbema_001.jpg/1280px-Meindert_Hobbema_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg/1280px-Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>Antoine van DYCK</t>
+  </si>
+  <si>
+    <t>Annibale CARRACI ou CARRACHE</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO ou CARAVAGE</t>
+  </si>
+  <si>
+    <t>Charles LE BRUN</t>
+  </si>
+  <si>
+    <t>David TENIERS LE JEUNE</t>
+  </si>
+  <si>
+    <t>Eustache LE SUEUR</t>
+  </si>
+  <si>
+    <t>Willem van de VELDE LE JEUNE</t>
+  </si>
+  <si>
+    <t>GUERCINO ou GUERCHIN</t>
   </si>
 </sst>
 </file>
@@ -844,10 +844,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>11</v>
@@ -861,112 +861,112 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="C9" s="4">
         <v>1643</v>
@@ -975,100 +975,100 @@
         <v>6</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>40</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>5</v>
@@ -1077,15 +1077,15 @@
         <v>6</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>7</v>
@@ -1094,219 +1094,219 @@
         <v>6</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C21" s="4">
         <v>1651</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C29" s="4">
         <v>1649</v>
@@ -1315,74 +1315,74 @@
         <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="3" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{BF908DEB-302B-4A7D-9647-D1EFA4FA35C0}"/>
-    <hyperlink ref="A3" r:id="rId2" display="https://upload.wikimedia.org/wikipedia/commons/a/ae/Portrait_de_Charles_1er%2C_roi_d%27Angleterre%2C_%C3%A0_la_chasse_-_Antoon_van_Dyck_-_Mus%C3%A9e_du_Louvre_Peintures_INV_1236_%3B_MR_666.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original" xr:uid="{B1DA1517-CFBD-43D9-993F-6C9F657DECB4}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{7E0DEBF1-9967-4A4C-8099-60B9DEB5D6A8}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{96AEEB4F-086F-426E-B93A-2DA57DE54BFE}"/>
-    <hyperlink ref="A6" r:id="rId5" xr:uid="{8D66B7E5-4F81-473E-BAC6-3A133A8BF0A1}"/>
-    <hyperlink ref="A7" r:id="rId6" xr:uid="{26C60298-1859-49FC-B93F-6E2DBE064D95}"/>
-    <hyperlink ref="A8" r:id="rId7" display="https://upload.wikimedia.org/wikipedia/commons/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{EF1DEDB6-C815-4BDA-9879-3384057FFBDB}"/>
-    <hyperlink ref="A9" r:id="rId8" xr:uid="{1A7A1C2D-9BDA-4D6C-AB0D-298B63D4B420}"/>
-    <hyperlink ref="A10" r:id="rId9" xr:uid="{E295B8A2-C5BB-45D7-9AA7-E002F85E21B1}"/>
-    <hyperlink ref="A11" r:id="rId10" xr:uid="{55E726A8-6C5A-40E3-B1C5-B4EC6C735238}"/>
-    <hyperlink ref="A12" r:id="rId11" xr:uid="{2AB88B44-F231-4B4B-A7BD-4C589B3E43E3}"/>
-    <hyperlink ref="A13" r:id="rId12" xr:uid="{5B67177B-3566-448C-82E8-B3E47FC7E769}"/>
-    <hyperlink ref="A14" r:id="rId13" xr:uid="{E1C8A8CF-4AE8-4C17-BE5B-9FAE82B663F7}"/>
-    <hyperlink ref="A15" r:id="rId14" xr:uid="{8D4F9315-2578-4A82-A162-B6F8D1439BCA}"/>
-    <hyperlink ref="A16" r:id="rId15" xr:uid="{636B89F5-0780-4E07-8ECA-A1510576ABCD}"/>
-    <hyperlink ref="A17" r:id="rId16" xr:uid="{9D3E1C27-FE83-4482-8C5F-CC33FCC1E2C6}"/>
-    <hyperlink ref="A18" r:id="rId17" xr:uid="{C423AE40-5C52-44E9-846A-DCBE38942E39}"/>
-    <hyperlink ref="A19" r:id="rId18" xr:uid="{39A0F762-D90E-4572-9DEC-9EA918318ACF}"/>
-    <hyperlink ref="A20" r:id="rId19" xr:uid="{854D64A5-0416-4CA8-BA54-6104DE34FE41}"/>
-    <hyperlink ref="A21" r:id="rId20" xr:uid="{360DE5AA-3E6B-4B70-92A1-E33A17D256DC}"/>
-    <hyperlink ref="A22" r:id="rId21" xr:uid="{9F33292D-E11B-47E3-A758-5369AF1AFBB7}"/>
-    <hyperlink ref="A23" r:id="rId22" xr:uid="{2BF6D38A-2C06-4EB1-83D9-ADA687CE29F2}"/>
-    <hyperlink ref="A24" r:id="rId23" xr:uid="{8AB4CB1D-C2C6-41EA-890E-ABACF970DD91}"/>
-    <hyperlink ref="A25" r:id="rId24" xr:uid="{01EA9FE3-3B2A-42AC-A1F3-B75B9ACC1DFF}"/>
-    <hyperlink ref="A26" r:id="rId25" xr:uid="{FA4FAF58-BD57-4E39-9226-854692AFB81E}"/>
-    <hyperlink ref="A27" r:id="rId26" xr:uid="{90544544-956B-488D-9781-06680F0DA998}"/>
-    <hyperlink ref="A28" r:id="rId27" xr:uid="{5F76217F-4F6B-4D31-BC66-876467E7E67C}"/>
-    <hyperlink ref="A29" r:id="rId28" xr:uid="{B20C8042-5197-411A-8C08-02B3412DF1B5}"/>
-    <hyperlink ref="A30" r:id="rId29" xr:uid="{30960AA4-BF0A-418D-B786-3593B23BD377}"/>
+    <hyperlink ref="A4" r:id="rId2" xr:uid="{7E0DEBF1-9967-4A4C-8099-60B9DEB5D6A8}"/>
+    <hyperlink ref="A5" r:id="rId3" xr:uid="{96AEEB4F-086F-426E-B93A-2DA57DE54BFE}"/>
+    <hyperlink ref="A6" r:id="rId4" xr:uid="{8D66B7E5-4F81-473E-BAC6-3A133A8BF0A1}"/>
+    <hyperlink ref="A7" r:id="rId5" xr:uid="{26C60298-1859-49FC-B93F-6E2DBE064D95}"/>
+    <hyperlink ref="A9" r:id="rId6" xr:uid="{1A7A1C2D-9BDA-4D6C-AB0D-298B63D4B420}"/>
+    <hyperlink ref="A11" r:id="rId7" xr:uid="{55E726A8-6C5A-40E3-B1C5-B4EC6C735238}"/>
+    <hyperlink ref="A12" r:id="rId8" xr:uid="{2AB88B44-F231-4B4B-A7BD-4C589B3E43E3}"/>
+    <hyperlink ref="A14" r:id="rId9" xr:uid="{E1C8A8CF-4AE8-4C17-BE5B-9FAE82B663F7}"/>
+    <hyperlink ref="A16" r:id="rId10" xr:uid="{636B89F5-0780-4E07-8ECA-A1510576ABCD}"/>
+    <hyperlink ref="A17" r:id="rId11" xr:uid="{9D3E1C27-FE83-4482-8C5F-CC33FCC1E2C6}"/>
+    <hyperlink ref="A18" r:id="rId12" xr:uid="{C423AE40-5C52-44E9-846A-DCBE38942E39}"/>
+    <hyperlink ref="A20" r:id="rId13" xr:uid="{854D64A5-0416-4CA8-BA54-6104DE34FE41}"/>
+    <hyperlink ref="A22" r:id="rId14" xr:uid="{9F33292D-E11B-47E3-A758-5369AF1AFBB7}"/>
+    <hyperlink ref="A26" r:id="rId15" xr:uid="{FA4FAF58-BD57-4E39-9226-854692AFB81E}"/>
+    <hyperlink ref="A27" r:id="rId16" xr:uid="{90544544-956B-488D-9781-06680F0DA998}"/>
+    <hyperlink ref="A28" r:id="rId17" xr:uid="{5F76217F-4F6B-4D31-BC66-876467E7E67C}"/>
+    <hyperlink ref="A29" r:id="rId18" xr:uid="{B20C8042-5197-411A-8C08-02B3412DF1B5}"/>
+    <hyperlink ref="A30" r:id="rId19" xr:uid="{30960AA4-BF0A-418D-B786-3593B23BD377}"/>
+    <hyperlink ref="A3" r:id="rId20" xr:uid="{C4F64B89-3774-43B7-8A0C-D3AC6A7B801B}"/>
+    <hyperlink ref="A8" r:id="rId21" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EA96BAF3-80FC-494A-8DDE-F14C0007C067}"/>
+    <hyperlink ref="A10" r:id="rId22" xr:uid="{95EACEF5-C850-4490-8856-9E46D689B4A3}"/>
+    <hyperlink ref="A13" r:id="rId23" xr:uid="{5C77EBF0-8891-4E82-8D7F-9B004EB4C4A4}"/>
+    <hyperlink ref="A15" r:id="rId24" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46AD3053-8E76-43A6-AB69-CD833A51875A}"/>
+    <hyperlink ref="A19" r:id="rId25" xr:uid="{16D10A9D-D8C9-4BAC-A8CC-9AF260054744}"/>
+    <hyperlink ref="A21" r:id="rId26" xr:uid="{F01A873E-A482-44E5-BB83-1042CBABBA22}"/>
+    <hyperlink ref="A23" r:id="rId27" xr:uid="{8C825FAF-497F-4651-B205-A8211FC58448}"/>
+    <hyperlink ref="A24" r:id="rId28" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6DF40185-37D0-4D2F-AD9B-D0D822645CEF}"/>
+    <hyperlink ref="A25" r:id="rId29" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg/1280px-Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{D99B6F1B-0559-45E5-9CE2-D6471924A44C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-17e-niveau1.xlsx
+++ b/quizzes/peinture-17e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF4616F-4A4F-4361-92B9-D04BD2125D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9064CFE0-C354-41FA-AD42-942B0432312C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="135">
   <si>
     <t>image</t>
   </si>
@@ -91,12 +91,6 @@
     <t>L'Immaculée Conception des Vénérables</t>
   </si>
   <si>
-    <t>1596-1597</t>
-  </si>
-  <si>
-    <t>Bacchus</t>
-  </si>
-  <si>
     <t>Galleria Nazionale d'Arte Antica, Rome</t>
   </si>
   <si>
@@ -316,9 +310,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/6/61/Murillo_immaculate_conception.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/1/1e/Bacchus_%28by_Michelangelo_Merisi_da_Caravaggio%29_%E2%80%93_Galleria_degli_Uffizi%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/6/60/Charles_Le_Brun_-_Pierre_S%C3%A9guier%2C_chancelier_de_France_%281655-1661%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -425,6 +416,15 @@
   </si>
   <si>
     <t>GUERCINO ou GUERCHIN</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/48/The_Calling_of_Saint_Matthew-Caravaggo_%281599-1600%29.jpg/1280px-The_Calling_of_Saint_Matthew-Caravaggo_%281599-1600%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>Eglise Saint-Louis-des-Français, Rome</t>
+  </si>
+  <si>
+    <t>La Vocation de saint Matthieu</t>
   </si>
 </sst>
 </file>
@@ -844,10 +844,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>11</v>
@@ -861,10 +861,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>14</v>
@@ -878,7 +878,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -895,7 +895,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>20</v>
@@ -912,61 +912,61 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>126</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1600</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C9" s="4">
         <v>1643</v>
@@ -975,100 +975,100 @@
         <v>6</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>5</v>
@@ -1077,15 +1077,15 @@
         <v>6</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>7</v>
@@ -1094,219 +1094,219 @@
         <v>6</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C21" s="4">
         <v>1651</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C29" s="4">
         <v>1649</v>
@@ -1315,74 +1315,77 @@
         <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E31">
+    <sortCondition ref="B2:B31"/>
+  </sortState>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{BF908DEB-302B-4A7D-9647-D1EFA4FA35C0}"/>
     <hyperlink ref="A4" r:id="rId2" xr:uid="{7E0DEBF1-9967-4A4C-8099-60B9DEB5D6A8}"/>
     <hyperlink ref="A5" r:id="rId3" xr:uid="{96AEEB4F-086F-426E-B93A-2DA57DE54BFE}"/>
-    <hyperlink ref="A6" r:id="rId4" xr:uid="{8D66B7E5-4F81-473E-BAC6-3A133A8BF0A1}"/>
-    <hyperlink ref="A7" r:id="rId5" xr:uid="{26C60298-1859-49FC-B93F-6E2DBE064D95}"/>
-    <hyperlink ref="A9" r:id="rId6" xr:uid="{1A7A1C2D-9BDA-4D6C-AB0D-298B63D4B420}"/>
-    <hyperlink ref="A11" r:id="rId7" xr:uid="{55E726A8-6C5A-40E3-B1C5-B4EC6C735238}"/>
-    <hyperlink ref="A12" r:id="rId8" xr:uid="{2AB88B44-F231-4B4B-A7BD-4C589B3E43E3}"/>
-    <hyperlink ref="A14" r:id="rId9" xr:uid="{E1C8A8CF-4AE8-4C17-BE5B-9FAE82B663F7}"/>
-    <hyperlink ref="A16" r:id="rId10" xr:uid="{636B89F5-0780-4E07-8ECA-A1510576ABCD}"/>
-    <hyperlink ref="A17" r:id="rId11" xr:uid="{9D3E1C27-FE83-4482-8C5F-CC33FCC1E2C6}"/>
-    <hyperlink ref="A18" r:id="rId12" xr:uid="{C423AE40-5C52-44E9-846A-DCBE38942E39}"/>
-    <hyperlink ref="A20" r:id="rId13" xr:uid="{854D64A5-0416-4CA8-BA54-6104DE34FE41}"/>
-    <hyperlink ref="A22" r:id="rId14" xr:uid="{9F33292D-E11B-47E3-A758-5369AF1AFBB7}"/>
-    <hyperlink ref="A26" r:id="rId15" xr:uid="{FA4FAF58-BD57-4E39-9226-854692AFB81E}"/>
-    <hyperlink ref="A27" r:id="rId16" xr:uid="{90544544-956B-488D-9781-06680F0DA998}"/>
-    <hyperlink ref="A28" r:id="rId17" xr:uid="{5F76217F-4F6B-4D31-BC66-876467E7E67C}"/>
-    <hyperlink ref="A29" r:id="rId18" xr:uid="{B20C8042-5197-411A-8C08-02B3412DF1B5}"/>
-    <hyperlink ref="A30" r:id="rId19" xr:uid="{30960AA4-BF0A-418D-B786-3593B23BD377}"/>
-    <hyperlink ref="A3" r:id="rId20" xr:uid="{C4F64B89-3774-43B7-8A0C-D3AC6A7B801B}"/>
-    <hyperlink ref="A8" r:id="rId21" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EA96BAF3-80FC-494A-8DDE-F14C0007C067}"/>
-    <hyperlink ref="A10" r:id="rId22" xr:uid="{95EACEF5-C850-4490-8856-9E46D689B4A3}"/>
-    <hyperlink ref="A13" r:id="rId23" xr:uid="{5C77EBF0-8891-4E82-8D7F-9B004EB4C4A4}"/>
-    <hyperlink ref="A15" r:id="rId24" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46AD3053-8E76-43A6-AB69-CD833A51875A}"/>
-    <hyperlink ref="A19" r:id="rId25" xr:uid="{16D10A9D-D8C9-4BAC-A8CC-9AF260054744}"/>
-    <hyperlink ref="A21" r:id="rId26" xr:uid="{F01A873E-A482-44E5-BB83-1042CBABBA22}"/>
-    <hyperlink ref="A23" r:id="rId27" xr:uid="{8C825FAF-497F-4651-B205-A8211FC58448}"/>
-    <hyperlink ref="A24" r:id="rId28" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6DF40185-37D0-4D2F-AD9B-D0D822645CEF}"/>
-    <hyperlink ref="A25" r:id="rId29" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg/1280px-Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{D99B6F1B-0559-45E5-9CE2-D6471924A44C}"/>
+    <hyperlink ref="A7" r:id="rId4" xr:uid="{26C60298-1859-49FC-B93F-6E2DBE064D95}"/>
+    <hyperlink ref="A9" r:id="rId5" xr:uid="{1A7A1C2D-9BDA-4D6C-AB0D-298B63D4B420}"/>
+    <hyperlink ref="A11" r:id="rId6" xr:uid="{55E726A8-6C5A-40E3-B1C5-B4EC6C735238}"/>
+    <hyperlink ref="A12" r:id="rId7" xr:uid="{2AB88B44-F231-4B4B-A7BD-4C589B3E43E3}"/>
+    <hyperlink ref="A14" r:id="rId8" xr:uid="{E1C8A8CF-4AE8-4C17-BE5B-9FAE82B663F7}"/>
+    <hyperlink ref="A16" r:id="rId9" xr:uid="{636B89F5-0780-4E07-8ECA-A1510576ABCD}"/>
+    <hyperlink ref="A17" r:id="rId10" xr:uid="{9D3E1C27-FE83-4482-8C5F-CC33FCC1E2C6}"/>
+    <hyperlink ref="A18" r:id="rId11" xr:uid="{C423AE40-5C52-44E9-846A-DCBE38942E39}"/>
+    <hyperlink ref="A20" r:id="rId12" xr:uid="{854D64A5-0416-4CA8-BA54-6104DE34FE41}"/>
+    <hyperlink ref="A22" r:id="rId13" xr:uid="{9F33292D-E11B-47E3-A758-5369AF1AFBB7}"/>
+    <hyperlink ref="A26" r:id="rId14" xr:uid="{FA4FAF58-BD57-4E39-9226-854692AFB81E}"/>
+    <hyperlink ref="A27" r:id="rId15" xr:uid="{90544544-956B-488D-9781-06680F0DA998}"/>
+    <hyperlink ref="A28" r:id="rId16" xr:uid="{5F76217F-4F6B-4D31-BC66-876467E7E67C}"/>
+    <hyperlink ref="A29" r:id="rId17" xr:uid="{B20C8042-5197-411A-8C08-02B3412DF1B5}"/>
+    <hyperlink ref="A30" r:id="rId18" xr:uid="{30960AA4-BF0A-418D-B786-3593B23BD377}"/>
+    <hyperlink ref="A3" r:id="rId19" xr:uid="{C4F64B89-3774-43B7-8A0C-D3AC6A7B801B}"/>
+    <hyperlink ref="A8" r:id="rId20" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EA96BAF3-80FC-494A-8DDE-F14C0007C067}"/>
+    <hyperlink ref="A10" r:id="rId21" xr:uid="{95EACEF5-C850-4490-8856-9E46D689B4A3}"/>
+    <hyperlink ref="A13" r:id="rId22" xr:uid="{5C77EBF0-8891-4E82-8D7F-9B004EB4C4A4}"/>
+    <hyperlink ref="A15" r:id="rId23" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46AD3053-8E76-43A6-AB69-CD833A51875A}"/>
+    <hyperlink ref="A19" r:id="rId24" xr:uid="{16D10A9D-D8C9-4BAC-A8CC-9AF260054744}"/>
+    <hyperlink ref="A21" r:id="rId25" xr:uid="{F01A873E-A482-44E5-BB83-1042CBABBA22}"/>
+    <hyperlink ref="A23" r:id="rId26" xr:uid="{8C825FAF-497F-4651-B205-A8211FC58448}"/>
+    <hyperlink ref="A24" r:id="rId27" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6DF40185-37D0-4D2F-AD9B-D0D822645CEF}"/>
+    <hyperlink ref="A25" r:id="rId28" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg/1280px-Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{D99B6F1B-0559-45E5-9CE2-D6471924A44C}"/>
+    <hyperlink ref="A6" r:id="rId29" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/48/The_Calling_of_Saint_Matthew-Caravaggo_%281599-1600%29.jpg/1280px-The_Calling_of_Saint_Matthew-Caravaggo_%281599-1600%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{92049190-CBB0-4FA3-B931-FE5A93CFE880}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-17e-niveau1.xlsx
+++ b/quizzes/peinture-17e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9064CFE0-C354-41FA-AD42-942B0432312C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A683B6A-6E87-4AC2-B230-3E7A2147D5F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="123">
   <si>
     <t>image</t>
   </si>
@@ -37,33 +37,30 @@
     <t>titre de l'œuvre</t>
   </si>
   <si>
+    <t>1630-1635</t>
+  </si>
+  <si>
     <t>1636-1638</t>
   </si>
   <si>
+    <t>Alte Pinakothek, Munich</t>
+  </si>
+  <si>
     <t>Musée du Louvre, Paris</t>
   </si>
   <si>
-    <t>1663</t>
-  </si>
-  <si>
     <t>Rijksmuseum, Amsterdam</t>
   </si>
   <si>
+    <t>1650</t>
+  </si>
+  <si>
     <t>National Gallery, Londres</t>
   </si>
   <si>
     <t>Museo del Prado, Madrid</t>
   </si>
   <si>
-    <t>1604</t>
-  </si>
-  <si>
-    <t>Galleria Doria Pamphilj, Rome</t>
-  </si>
-  <si>
-    <t>Paysage avec la fuite en Égypte</t>
-  </si>
-  <si>
     <t>1635</t>
   </si>
   <si>
@@ -82,27 +79,57 @@
     <t>Judith décapitant Holopherne</t>
   </si>
   <si>
+    <t>1610</t>
+  </si>
+  <si>
+    <t>Schloss Weissenstein, Pommersfelden</t>
+  </si>
+  <si>
+    <t>Suzanne et les vieillards</t>
+  </si>
+  <si>
     <t>Bartolomé Esteban Murillo</t>
   </si>
   <si>
-    <t>1678</t>
-  </si>
-  <si>
-    <t>L'Immaculée Conception des Vénérables</t>
-  </si>
-  <si>
-    <t>Galleria Nazionale d'Arte Antica, Rome</t>
+    <t>1645-1646</t>
+  </si>
+  <si>
+    <t>Les Enfants mangeant des raisins et un melon</t>
+  </si>
+  <si>
+    <t>Église Saint-Louis-des-Français, Rome</t>
+  </si>
+  <si>
+    <t>La Vocation de saint Matthieu</t>
   </si>
   <si>
     <t>Mauritshuis, La Haye</t>
   </si>
   <si>
+    <t>Vue de Delft</t>
+  </si>
+  <si>
+    <t>Autoportrait</t>
+  </si>
+  <si>
+    <t>1660-1661</t>
+  </si>
+  <si>
+    <t>Château de Versailles, Versailles</t>
+  </si>
+  <si>
     <t>1655-1661</t>
   </si>
   <si>
     <t>Portrait du chancelier Séguier</t>
   </si>
   <si>
+    <t>1678-1684</t>
+  </si>
+  <si>
+    <t>La Galerie des Glaces (plafond)</t>
+  </si>
+  <si>
     <t>Claude Lorrain</t>
   </si>
   <si>
@@ -112,12 +139,15 @@
     <t>Le Débarquement de Cléopâtre à Tarse</t>
   </si>
   <si>
+    <t>1648</t>
+  </si>
+  <si>
+    <t>Paysage avec l'embarquement de la reine de Saba</t>
+  </si>
+  <si>
     <t>1642</t>
   </si>
   <si>
-    <t>Le Fumeur</t>
-  </si>
-  <si>
     <t>Diego Velázquez</t>
   </si>
   <si>
@@ -127,19 +157,13 @@
     <t>Les Ménines</t>
   </si>
   <si>
-    <t>1652-1655</t>
-  </si>
-  <si>
-    <t>Melpomène, Érato et Polymnie</t>
-  </si>
-  <si>
-    <t>Francisco de Zurbarán</t>
-  </si>
-  <si>
-    <t>1635-1640</t>
-  </si>
-  <si>
-    <t>L'Agneau de Dieu (Agnus Dei)</t>
+    <t>1634-1635</t>
+  </si>
+  <si>
+    <t>La Reddition de Breda (Les Lances)</t>
+  </si>
+  <si>
+    <t>1645-1648</t>
   </si>
   <si>
     <t>Frans Hals</t>
@@ -154,82 +178,31 @@
     <t>Le Cavalier riant</t>
   </si>
   <si>
-    <t>Gabriel Metsu</t>
-  </si>
-  <si>
-    <t>1664-1666</t>
-  </si>
-  <si>
-    <t>National Gallery of Ireland, Dublin</t>
-  </si>
-  <si>
-    <t>Femme lisant une lettre</t>
-  </si>
-  <si>
     <t>Georges de La Tour</t>
   </si>
   <si>
     <t>Le Tricheur à l'as de carreau</t>
   </si>
   <si>
-    <t>1640-1645</t>
-  </si>
-  <si>
-    <t>Gerard Dou</t>
-  </si>
-  <si>
-    <t>La Femme hydropique</t>
-  </si>
-  <si>
-    <t>1658</t>
-  </si>
-  <si>
-    <t>1665</t>
-  </si>
-  <si>
-    <t>1618-1622</t>
-  </si>
-  <si>
-    <t>Et in Arcadia ego (Les Bergers d'Arcadie)</t>
-  </si>
-  <si>
-    <t>Hyacinthe Rigaud</t>
-  </si>
-  <si>
-    <t>1698</t>
-  </si>
-  <si>
-    <t>Musée Rigaud, Perpignan</t>
-  </si>
-  <si>
-    <t>Autoportrait au turban</t>
-  </si>
-  <si>
-    <t>1689</t>
-  </si>
-  <si>
-    <t>Jacob Jordaens</t>
-  </si>
-  <si>
-    <t>Le Roi boit !</t>
-  </si>
-  <si>
-    <t>1638</t>
-  </si>
-  <si>
-    <t>Jacob van Ruisdael</t>
-  </si>
-  <si>
-    <t>1670</t>
-  </si>
-  <si>
-    <t>Le Moulin de Wijk bij Duurstede</t>
-  </si>
-  <si>
-    <t>Jan van Goyen</t>
-  </si>
-  <si>
-    <t>Vue de Dordrecht</t>
+    <t>Musée des Beaux-Arts, Rennes</t>
+  </si>
+  <si>
+    <t>Le Nouveau-né</t>
+  </si>
+  <si>
+    <t>Casino dell'Aurora, Rome</t>
+  </si>
+  <si>
+    <t>Guido Reni</t>
+  </si>
+  <si>
+    <t>1613-1614</t>
+  </si>
+  <si>
+    <t>L'Aurore (plafond du Casino Rospigliosi)</t>
+  </si>
+  <si>
+    <t>Musée de l'Ermitage, Saint-Pétersbourg</t>
   </si>
   <si>
     <t>1641</t>
@@ -238,13 +211,25 @@
     <t>Johannes Vermeer</t>
   </si>
   <si>
-    <t>La Jeune Fille à la perle</t>
-  </si>
-  <si>
-    <t>Meindert Hobbema</t>
-  </si>
-  <si>
-    <t>L'Avenue à Middelharnis</t>
+    <t>1658-1661</t>
+  </si>
+  <si>
+    <t>La Laitière</t>
+  </si>
+  <si>
+    <t>1632</t>
+  </si>
+  <si>
+    <t>Louis Le Nain</t>
+  </si>
+  <si>
+    <t>Le Repas de paysans</t>
+  </si>
+  <si>
+    <t>La Forge</t>
+  </si>
+  <si>
+    <t>Le Jugement de Salomon</t>
   </si>
   <si>
     <t>Nicolas Poussin</t>
@@ -259,28 +244,16 @@
     <t>Peter Paul Rubens</t>
   </si>
   <si>
-    <t>1612-1614</t>
-  </si>
-  <si>
     <t>Cathédrale Notre-Dame, Anvers</t>
   </si>
   <si>
-    <t>La Descente de croix</t>
-  </si>
-  <si>
-    <t>Philippe de Champaigne</t>
-  </si>
-  <si>
-    <t>Musée des Beaux-Arts, Caen</t>
-  </si>
-  <si>
-    <t>Le Voeu de Louis XIII</t>
-  </si>
-  <si>
-    <t>Pieter de Hooch</t>
-  </si>
-  <si>
-    <t>La Cour d'une maison à Delft</t>
+    <t>1610-1611</t>
+  </si>
+  <si>
+    <t>L'Érection de la croix</t>
+  </si>
+  <si>
+    <t>Les Trois Grâces</t>
   </si>
   <si>
     <t>Rembrandt van Rijn</t>
@@ -289,7 +262,7 @@
     <t>La Ronde de nuit</t>
   </si>
   <si>
-    <t>Salomon van Ruysdael</t>
+    <t>La Leçon d'anatomie du docteur Tulp</t>
   </si>
   <si>
     <t>Simon Vouet</t>
@@ -298,70 +271,43 @@
     <t>La Présentation au Temple</t>
   </si>
   <si>
-    <t>Le Canon de salut</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/92/Annibale_Carracci_003.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/b/b0/GENTILESCHI_Judith.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/6/61/Murillo_immaculate_conception.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/0/04/Susanna_and_the_Elders_%281610%29%2C_Artemisia_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/7b/Bartolom%C3%A9_Esteban_Perez_Murillo_-_Grape_and_Melon_Eaters.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/77/0_%27La_Vocation_de_saint_Matthieu%27_de_Le_Caravage_-_fr2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/6/60/Charles_Le_Brun_-_Pierre_S%C3%A9guier%2C_chancelier_de_France_%281655-1661%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/0/0a/David_Teniers_%28II%29_-_Smoker_Leaning_his_Elbow_on_a_Table_-_WGA22080.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/ad/Le_Sueur%2C_Eustache_-_Melpom%C3%A8ne%2C_%C3%89rato_et_Polymnie_-_1652_-_1655.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/e/ef/Francisco_de_Zurbar%C3%A1n_006.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/f/fe/Woman_Reading_a_Letter_by_Gabri%C3%ABl_Metsu.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/9f/Gerard_Dou_-_The_Dropsical_Woman_-_WGA06647.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/b/b9/Et-in-Arcadia-ego.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/8d/Autoportrait_au_turban_%28Perpignan%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/7/74/Jacob_Isaacksz._van_Ruisdael_-_Le_Moulin_de_Wijk-bij-Duurstede.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Musée de Dordrecht</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0f/1665_Girl_with_a_Pearl_Earring.jpg/1920px-1665_Girl_with_a_Pearl_Earring.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/82/Le_v%C5%93u_de_Louis_XIII.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/c/c2/Pieter_de_Hooch_-_The_Courtyard_of_a_House_in_Delft.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/a/a3/Guido_Reni_-_Aurora_-_WGA19273.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/5/5a/Johannes_Vermeer_-_De_melkmeid.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c7/Le_Nain_-_Repas_de_paysans_%281642%29.jpg/1280px-Le_Nain_-_Repas_de_paysans_%281642%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a5/%22La_forge%22%2C_Louis_Le_Nain%2C_vers_1640-1642._Mus%C3%A9e_du_Louvre._%2835366251024%29.jpg/1920px-%22La_forge%22%2C_Louis_Le_Nain%2C_vers_1640-1642._Mus%C3%A9e_du_Louvre._%2835366251024%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/d/d9/Nicolas_Poussin_078.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/The_Nightwatch_by_Rembrandt_-_Rijksmuseum.jpg/3840px-The_Nightwatch_by_Rembrandt_-_Rijksmuseum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Paysage fluvial avec ferry </t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/7/78/Rivierlandschap_met_een_veerboot_Rijksmuseum_SK-C-1698.jpeg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/9/91/Simon_Vouet_-_Presentation_in_the_Temple_-_WGA25366.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/e/ed/Het_Kanonschot_-_Canon_fired_%28Willem_van_de_Velde_II%2C_1707%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+    <t>Petit-déjeuner avec un crabe</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/6/6e/Van_Dyck_Charles_I_1635.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
@@ -370,61 +316,79 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg/1280px-Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f1/Chateau_Versailles_Galerie_des_Glaces.jpg/1280px-Chateau_Versailles_Galerie_des_Glaces.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/6/69/Analyasis_of_Las_Meninas.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg/1280px-Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Frans_Hals_%E2%80%93_The_Laughing_Cavalier.jpg/960px-Frans_Hals_%E2%80%93_The_Laughing_Cavalier.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/b/bc/Jacob_Jordaens_-_The_Bean_King_%28Louvre%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/01/Goyen_1651_View_of_Dordrecht.jpg/1280px-Goyen_1651_View_of_Dordrecht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/Meindert_Hobbema_001.jpg/1280px-Meindert_Hobbema_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg/1280px-Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c5/Johannes_Vermeer_-_View_of_Delft_-_92_-_Mauritshuis.jpg/1280px-Johannes_Vermeer_-_View_of_Delft_-_92_-_Mauritshuis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg/1280px-Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg/1280px-Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9c/Rubens%2C_Peter_Paul_-_The_Three_Graces.jpg/960px-Rubens%2C_Peter_Paul_-_The_Three_Graces.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Rembrandt_-_The_Anatomy_Lesson_of_Dr_Nicolaes_Tulp.jpg/1280px-Rembrandt_-_The_Anatomy_Lesson_of_Dr_Nicolaes_Tulp.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Heda_hermitage.jpg/1280px-Heda_hermitage.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
     <t>Antoine van DYCK</t>
   </si>
   <si>
-    <t>Annibale CARRACI ou CARRACHE</t>
-  </si>
-  <si>
     <t>CARAVAGGIO ou CARAVAGE</t>
   </si>
   <si>
     <t>Charles LE BRUN</t>
   </si>
   <si>
-    <t>David TENIERS LE JEUNE</t>
-  </si>
-  <si>
-    <t>Eustache LE SUEUR</t>
-  </si>
-  <si>
-    <t>Willem van de VELDE LE JEUNE</t>
-  </si>
-  <si>
-    <t>GUERCINO ou GUERCHIN</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/48/The_Calling_of_Saint_Matthew-Caravaggo_%281599-1600%29.jpg/1280px-The_Calling_of_Saint_Matthew-Caravaggo_%281599-1600%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
-  </si>
-  <si>
-    <t>Eglise Saint-Louis-des-Français, Rome</t>
-  </si>
-  <si>
-    <t>La Vocation de saint Matthieu</t>
+    <t>Willem CLAESZOON HEDA</t>
+  </si>
+  <si>
+    <t>Le Souper à Emmaüs</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c0/Supper_at_Emmaus-Caravaggio_%281601%29.jpg/1280px-Supper_at_Emmaus-Caravaggio_%281601%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Valentin de Boulogne</t>
+  </si>
+  <si>
+    <t>Gian Lorenzo Bernini</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d5/Gian_Lorenzo_Bernini%2C_self-portrait%2C_c1623.jpg/960px-Gian_Lorenzo_Bernini%2C_self-portrait%2C_c1623.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Galerie Borghese, Rome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autoportrait </t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/8/8a/Valentin_de_Boulogne%2C_Judgment_of_Solomon_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
 </sst>
 </file>
@@ -458,7 +422,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -475,8 +439,14 @@
         <fgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -499,17 +469,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -820,7 +812,7 @@
   <cols>
     <col min="1" max="1" width="77.85546875" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="3" max="3" width="19" style="11" customWidth="1"/>
     <col min="4" max="4" width="48.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="64.7109375" customWidth="1"/>
   </cols>
@@ -832,7 +824,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -843,445 +835,445 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="A2" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>13</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C6" s="4">
         <v>1600</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>133</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>134</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>25</v>
+        <v>112</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1601</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>26</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>113</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="8" customFormat="1">
+      <c r="A9" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="7" customFormat="1">
+      <c r="A10" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C9" s="4">
-        <v>1643</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="3" t="s">
+      <c r="B10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="7" customFormat="1">
+      <c r="A11" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="B11" s="6" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="C11" s="10" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="D11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="2" t="s">
+    </row>
+    <row r="12" spans="1:5" s="7" customFormat="1">
+      <c r="A12" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="C12" s="10" t="s">
         <v>43</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="7" customFormat="1">
+      <c r="A13" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>5</v>
+        <v>52</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>7</v>
+        <v>52</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>55</v>
+        <v>118</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1623</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>50</v>
+      <c r="C19" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" s="4">
-        <v>1651</v>
+        <v>66</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>53</v>
+        <v>78</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1289,103 +1281,104 @@
         <v>109</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>30</v>
+        <v>78</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" s="4">
-        <v>1649</v>
+        <v>81</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>70</v>
+        <v>117</v>
+      </c>
+      <c r="C30" s="4">
+        <v>1625</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>66</v>
+        <v>114</v>
+      </c>
+      <c r="C31" s="4">
+        <v>1648</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E31">
-    <sortCondition ref="B2:B31"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E203">
+    <sortCondition ref="B2:B203"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{BF908DEB-302B-4A7D-9647-D1EFA4FA35C0}"/>
-    <hyperlink ref="A4" r:id="rId2" xr:uid="{7E0DEBF1-9967-4A4C-8099-60B9DEB5D6A8}"/>
-    <hyperlink ref="A5" r:id="rId3" xr:uid="{96AEEB4F-086F-426E-B93A-2DA57DE54BFE}"/>
-    <hyperlink ref="A7" r:id="rId4" xr:uid="{26C60298-1859-49FC-B93F-6E2DBE064D95}"/>
-    <hyperlink ref="A9" r:id="rId5" xr:uid="{1A7A1C2D-9BDA-4D6C-AB0D-298B63D4B420}"/>
-    <hyperlink ref="A11" r:id="rId6" xr:uid="{55E726A8-6C5A-40E3-B1C5-B4EC6C735238}"/>
-    <hyperlink ref="A12" r:id="rId7" xr:uid="{2AB88B44-F231-4B4B-A7BD-4C589B3E43E3}"/>
-    <hyperlink ref="A14" r:id="rId8" xr:uid="{E1C8A8CF-4AE8-4C17-BE5B-9FAE82B663F7}"/>
-    <hyperlink ref="A16" r:id="rId9" xr:uid="{636B89F5-0780-4E07-8ECA-A1510576ABCD}"/>
-    <hyperlink ref="A17" r:id="rId10" xr:uid="{9D3E1C27-FE83-4482-8C5F-CC33FCC1E2C6}"/>
-    <hyperlink ref="A18" r:id="rId11" xr:uid="{C423AE40-5C52-44E9-846A-DCBE38942E39}"/>
-    <hyperlink ref="A20" r:id="rId12" xr:uid="{854D64A5-0416-4CA8-BA54-6104DE34FE41}"/>
-    <hyperlink ref="A22" r:id="rId13" xr:uid="{9F33292D-E11B-47E3-A758-5369AF1AFBB7}"/>
-    <hyperlink ref="A26" r:id="rId14" xr:uid="{FA4FAF58-BD57-4E39-9226-854692AFB81E}"/>
-    <hyperlink ref="A27" r:id="rId15" xr:uid="{90544544-956B-488D-9781-06680F0DA998}"/>
-    <hyperlink ref="A28" r:id="rId16" xr:uid="{5F76217F-4F6B-4D31-BC66-876467E7E67C}"/>
-    <hyperlink ref="A29" r:id="rId17" xr:uid="{B20C8042-5197-411A-8C08-02B3412DF1B5}"/>
-    <hyperlink ref="A30" r:id="rId18" xr:uid="{30960AA4-BF0A-418D-B786-3593B23BD377}"/>
-    <hyperlink ref="A3" r:id="rId19" xr:uid="{C4F64B89-3774-43B7-8A0C-D3AC6A7B801B}"/>
-    <hyperlink ref="A8" r:id="rId20" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EA96BAF3-80FC-494A-8DDE-F14C0007C067}"/>
-    <hyperlink ref="A10" r:id="rId21" xr:uid="{95EACEF5-C850-4490-8856-9E46D689B4A3}"/>
-    <hyperlink ref="A13" r:id="rId22" xr:uid="{5C77EBF0-8891-4E82-8D7F-9B004EB4C4A4}"/>
-    <hyperlink ref="A15" r:id="rId23" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46AD3053-8E76-43A6-AB69-CD833A51875A}"/>
-    <hyperlink ref="A19" r:id="rId24" xr:uid="{16D10A9D-D8C9-4BAC-A8CC-9AF260054744}"/>
-    <hyperlink ref="A21" r:id="rId25" xr:uid="{F01A873E-A482-44E5-BB83-1042CBABBA22}"/>
-    <hyperlink ref="A23" r:id="rId26" xr:uid="{8C825FAF-497F-4651-B205-A8211FC58448}"/>
-    <hyperlink ref="A24" r:id="rId27" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6DF40185-37D0-4D2F-AD9B-D0D822645CEF}"/>
-    <hyperlink ref="A25" r:id="rId28" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg/1280px-Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{D99B6F1B-0559-45E5-9CE2-D6471924A44C}"/>
-    <hyperlink ref="A6" r:id="rId29" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/48/The_Calling_of_Saint_Matthew-Caravaggo_%281599-1600%29.jpg/1280px-The_Calling_of_Saint_Matthew-Caravaggo_%281599-1600%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{92049190-CBB0-4FA3-B931-FE5A93CFE880}"/>
+    <hyperlink ref="A5" r:id="rId1" xr:uid="{B1D18D5B-F033-4CBC-8258-80D80B3D6B1A}"/>
+    <hyperlink ref="A6" r:id="rId2" xr:uid="{72C00A77-DE47-4350-ABDF-53A01568DB8C}"/>
+    <hyperlink ref="A8" r:id="rId3" xr:uid="{26C60298-1859-49FC-B93F-6E2DBE064D95}"/>
+    <hyperlink ref="A19" r:id="rId4" xr:uid="{FDEB65E8-E3C9-4173-A3A5-699B556167FB}"/>
+    <hyperlink ref="A21" r:id="rId5" xr:uid="{C2924DD1-C68C-444A-A0E3-59C8E373AD89}"/>
+    <hyperlink ref="A24" r:id="rId6" xr:uid="{7D7AB562-1695-44D3-9302-EB9B70CAA7E3}"/>
+    <hyperlink ref="A27" r:id="rId7" xr:uid="{5F76217F-4F6B-4D31-BC66-876467E7E67C}"/>
+    <hyperlink ref="A29" r:id="rId8" xr:uid="{30960AA4-BF0A-418D-B786-3593B23BD377}"/>
+    <hyperlink ref="A2" r:id="rId9" xr:uid="{945251CC-E6AD-4661-9571-02B7C81C2515}"/>
+    <hyperlink ref="A10" r:id="rId10" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{596E240E-7D53-4A32-9D33-569DA93A4937}"/>
+    <hyperlink ref="A12" r:id="rId11" xr:uid="{EF15C00B-27CF-44B6-8670-F310C1BB94A2}"/>
+    <hyperlink ref="A14" r:id="rId12" xr:uid="{59CEEA06-FA81-4ACE-8191-838FE9BA1BF7}"/>
+    <hyperlink ref="A16" r:id="rId13" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg/1280px-Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{10E006E8-2443-4060-9149-E3123D594459}"/>
+    <hyperlink ref="A20" r:id="rId14" xr:uid="{072FFDC6-2747-4BB4-BC37-0C70594E6F4D}"/>
+    <hyperlink ref="A23" r:id="rId15" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06C35A77-A512-486F-96AF-3B12DCA46F8F}"/>
+    <hyperlink ref="A25" r:id="rId16" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg/1280px-Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{975F1E1C-791A-4C4E-BECF-5701732F6721}"/>
+    <hyperlink ref="A26" r:id="rId17" xr:uid="{6F236C01-0CD5-413D-AAF1-D13121442DC4}"/>
+    <hyperlink ref="A28" r:id="rId18" xr:uid="{1C87A638-94E8-40B9-A0F1-C41FE40A0E7B}"/>
+    <hyperlink ref="A18" r:id="rId19" xr:uid="{7E575697-1670-41B2-BC75-9872FD034F04}"/>
+    <hyperlink ref="A15" r:id="rId20" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{78A42547-C969-4BBC-BDEF-3E15484B20A9}"/>
+    <hyperlink ref="A7" r:id="rId21" xr:uid="{313F2464-066F-4F8B-B7A6-8668093EF425}"/>
+    <hyperlink ref="A31" r:id="rId22" xr:uid="{DBF9950D-25AB-4896-9E4E-6E334EF854EB}"/>
+    <hyperlink ref="A13" r:id="rId23" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg/1280px-Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{57BDA7C2-2097-4285-8501-5706AF6C54CB}"/>
+    <hyperlink ref="A3" r:id="rId24" xr:uid="{7E0DEBF1-9967-4A4C-8099-60B9DEB5D6A8}"/>
+    <hyperlink ref="A4" r:id="rId25" xr:uid="{546CD3A0-4594-432F-814F-E62DAAAC6D34}"/>
+    <hyperlink ref="A9" r:id="rId26" xr:uid="{4C18F5D5-E2D3-4F40-B1CB-F3145EB601CB}"/>
+    <hyperlink ref="A11" r:id="rId27" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg/1280px-Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EBCA20AC-1D38-4222-AB4E-BF68B3C90D3C}"/>
+    <hyperlink ref="A17" r:id="rId28" xr:uid="{81C130C2-F590-4B7C-B698-9BF922FBB6C2}"/>
+    <hyperlink ref="A30" r:id="rId29" xr:uid="{60666AA9-3185-402A-BF30-FC338B38795C}"/>
+    <hyperlink ref="A22" r:id="rId30" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a5/%22La_forge%22%2C_Louis_Le_Nain%2C_vers_1640-1642._Mus%C3%A9e_du_Louvre._%2835366251024%29.jpg/1920px-%22La_forge%22%2C_Louis_Le_Nain%2C_vers_1640-1642._Mus%C3%A9e_du_Louvre._%2835366251024%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E12B8118-0F45-4A7E-923D-7ECB8B035284}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-17e-niveau1.xlsx
+++ b/quizzes/peinture-17e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4CF03C7-7486-464B-A524-4DC867F4C5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3629918-0451-470F-A303-DA948ECD6A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="186">
   <si>
     <t>image</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Dimensions</t>
   </si>
   <si>
+    <t>Nationalité</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/6/6e/Van_Dyck_Charles_I_1635.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>266 × 207 cm</t>
   </si>
   <si>
+    <t>flamande (Belgique)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/b/b0/GENTILESCHI_Judith.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
@@ -91,6 +97,9 @@
     <t>146,5 × 108 cm</t>
   </si>
   <si>
+    <t>italienne</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/0/04/Susanna_and_the_Elders_%281610%29%2C_Artemisia_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -127,6 +136,9 @@
     <t>146 × 104 cm</t>
   </si>
   <si>
+    <t>espagnole</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/7/77/0_%27La_Vocation_de_saint_Matthieu%27_de_Le_Caravage_-_fr2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -175,6 +187,9 @@
     <t>295 × 351 cm</t>
   </si>
   <si>
+    <t>française</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f1/Chateau_Versailles_Galerie_des_Glaces.jpg/1280px-Chateau_Versailles_Galerie_des_Glaces.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -275,6 +290,9 @@
   </si>
   <si>
     <t>83 × 67,3 cm</t>
+  </si>
+  <si>
+    <t>hollandaise (Pays-Bas)</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
@@ -679,7 +697,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1020,816 +1038,879 @@
       <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="7"/>
+        <v>24</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="G4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="7"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="7"/>
+        <v>37</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C6" s="6">
         <v>1600</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" s="7"/>
+        <v>44</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C7" s="6">
         <v>1601</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>39</v>
-      </c>
       <c r="G7" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="7"/>
+        <v>48</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" s="7"/>
+        <v>54</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1">
       <c r="A9" s="4" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>49</v>
-      </c>
       <c r="G9" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" s="7"/>
     </row>
     <row r="10" spans="1:9" s="1" customFormat="1">
       <c r="A10" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I10" s="7"/>
+        <v>67</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="11" spans="1:9" s="1" customFormat="1">
       <c r="A11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>58</v>
-      </c>
       <c r="C11" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I11" s="7"/>
+        <v>71</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="12" spans="1:9" s="1" customFormat="1">
       <c r="A12" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="I12" s="7"/>
+        <v>78</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="13" spans="1:9" s="1" customFormat="1">
       <c r="A13" s="4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>70</v>
-      </c>
       <c r="E13" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I13" s="7"/>
+        <v>82</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I14" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="I15" s="7"/>
+        <v>96</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="I16" s="7"/>
+        <v>101</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C17" s="6">
         <v>1623</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="I17" s="7"/>
+        <v>107</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="4" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="I18" s="7"/>
+        <v>115</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="4" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="I19" s="7"/>
+        <v>122</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="C20" s="6" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="I20" s="7"/>
+        <v>127</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="I21" s="7"/>
+        <v>133</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="I22" s="7"/>
+        <v>137</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="I23" s="7"/>
+        <v>143</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="I24" s="7"/>
+        <v>147</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="I25" s="7"/>
+        <v>155</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="I26" s="7"/>
+        <v>160</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="4" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I27" s="7"/>
+        <v>165</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="4" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="I28" s="7"/>
+        <v>169</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="4" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="I29" s="7"/>
+        <v>174</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="4" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C30" s="6">
         <v>1625</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="I30" s="7"/>
+        <v>179</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="4" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C31" s="6">
         <v>1648</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="I31" s="7"/>
+        <v>185</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>90</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
